--- a/study_case_model/smaller_network/scenario_variables/demand_scenarios111.xlsx
+++ b/study_case_model/smaller_network/scenario_variables/demand_scenarios111.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,195 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Equinor Energy AS</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ZEEBRUGGE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Vår Energi ASA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Equinor Energy AS</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST.FERGUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Vår Energi ASA</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Equinor Energy AS</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DORNUM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Vår Energi ASA</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/study_case_model/smaller_network/scenario_variables/demand_scenarios111.xlsx
+++ b/study_case_model/smaller_network/scenario_variables/demand_scenarios111.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,8 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ZEEBRUGGE</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -473,7 +471,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>20095.49522552418</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +481,8 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ZEEBRUGGE</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -504,10 +500,8 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ZEEBRUGGE</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -515,132 +509,6 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ST.FERGUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Equinor Energy AS</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ST.FERGUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SHELL</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ST.FERGUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Vår Energi ASA</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DORNUM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Equinor Energy AS</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DORNUM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SHELL</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DORNUM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Vår Energi ASA</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
         <v>0</v>
       </c>
     </row>
